--- a/Tratamento/src/Dados_limpos/novos/limpo_cobasi_20260803_205444.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_cobasi_20260803_205444.xlsx
@@ -5230,7 +5230,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5452,7 +5452,7 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5674,7 +5674,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5896,7 +5896,7 @@
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_cobasi_20260803_205444.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_cobasi_20260803_205444.xlsx
@@ -5230,7 +5230,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5452,7 +5452,7 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5674,7 +5674,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5896,7 +5896,7 @@
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
